--- a/data/trans_orig/IQ2608_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37063</t>
+          <t>37912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31811</t>
+          <t>31152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48857</t>
+          <t>48916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57632</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81375</t>
+          <t>81446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>35401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>53290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>57739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80942</t>
+          <t>80524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106119</t>
+          <t>105398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40667</t>
+          <t>41833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>58158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86205</t>
+          <t>84870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112587</t>
+          <t>110837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>39789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59096</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58109</t>
+          <t>58897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80273</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>104813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134958</t>
+          <t>133522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>50302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>69652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>70232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106364</t>
+          <t>105218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135825</t>
+          <t>134478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44377</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64190</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>68198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>96518</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124698</t>
+          <t>124705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>31891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49084</t>
+          <t>48900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47857</t>
+          <t>48338</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75637</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99012</t>
+          <t>99246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50253</t>
+          <t>50369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52517</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>74715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96913</t>
+          <t>96530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36061</t>
+          <t>36383</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>55941</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>78908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>50079</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73312</t>
+          <t>73308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65645</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88263</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>122809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155939</t>
+          <t>157520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64666</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88766</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>55492</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75561</t>
+          <t>76344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>126475</t>
+          <t>127326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158593</t>
+          <t>158722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53301</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55095</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74437</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101784</t>
+          <t>101295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>26090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>43357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162088</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199008</t>
+          <t>197897</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214368</t>
+          <t>211842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>252974</t>
+          <t>252072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>385533</t>
+          <t>388284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>440160</t>
+          <t>440515</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203665</t>
+          <t>205280</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>243026</t>
+          <t>243486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>236698</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>411833</t>
+          <t>411229</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>466931</t>
+          <t>466654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>157900</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>192901</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172351</t>
+          <t>170047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>209517</t>
+          <t>207319</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>339370</t>
+          <t>337716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>393533</t>
+          <t>389525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>66268</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>101402</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>135665</t>
+          <t>135529</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>65021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>84648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58829</t>
+          <t>58683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79853</t>
+          <t>79316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>129540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158113</t>
+          <t>159513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>50488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>43213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63931</t>
+          <t>63075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>79154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107418</t>
+          <t>106594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>41243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88770</t>
+          <t>88343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112106</t>
+          <t>112272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>105530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127373</t>
+          <t>128355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200285</t>
+          <t>201309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233942</t>
+          <t>234462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52921</t>
+          <t>53527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72735</t>
+          <t>73783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81522</t>
+          <t>79198</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115181</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>146772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50382</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65920</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84378</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>63577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84715</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135336</t>
+          <t>136364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164234</t>
+          <t>165346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>48153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>71093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>97096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54514</t>
+          <t>55042</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96365</t>
+          <t>95828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121737</t>
+          <t>119144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103054</t>
+          <t>102658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126722</t>
+          <t>125467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204065</t>
+          <t>205368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238608</t>
+          <t>239017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>47789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>69226</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42624</t>
+          <t>41929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62216</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96132</t>
+          <t>94233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126738</t>
+          <t>125676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>337852</t>
+          <t>336594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>379282</t>
+          <t>380660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351858</t>
+          <t>352353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>397140</t>
+          <t>397916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>699465</t>
+          <t>702733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>761755</t>
+          <t>764947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>180328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>216773</t>
+          <t>219391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>197957</t>
+          <t>196397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>239394</t>
+          <t>239696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391886</t>
+          <t>391968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>450580</t>
+          <t>449388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96957</t>
+          <t>96414</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>91826</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>140054</t>
+          <t>140473</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>180758</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44514</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44526</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>49342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>68239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80710</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113857</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142662</t>
+          <t>141917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51566</t>
+          <t>51302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92710</t>
+          <t>93131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119888</t>
+          <t>119951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84358</t>
+          <t>84181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105923</t>
+          <t>105490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85958</t>
+          <t>86063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110275</t>
+          <t>110734</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176673</t>
+          <t>176945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208532</t>
+          <t>208741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>73619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96576</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141857</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172552</t>
+          <t>173248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>31862</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58911</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66120</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84215</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80642</t>
+          <t>79551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130135</t>
+          <t>132124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>158975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53885</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71477</t>
+          <t>71946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>61684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82851</t>
+          <t>82219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121598</t>
+          <t>121524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149795</t>
+          <t>149003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90153</t>
+          <t>89705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68712</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91731</t>
+          <t>90725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>142100</t>
+          <t>141387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173730</t>
+          <t>173928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>83873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66237</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>89374</t>
+          <t>89456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133870</t>
+          <t>133046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166041</t>
+          <t>167050</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>36757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66736</t>
+          <t>66998</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43496</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>283203</t>
+          <t>287298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>326179</t>
+          <t>329408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>295362</t>
+          <t>294459</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>338142</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>595891</t>
+          <t>592177</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>655535</t>
+          <t>652926</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>233789</t>
+          <t>231566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272305</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>275937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>318816</t>
+          <t>320255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>522359</t>
+          <t>515062</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>582185</t>
+          <t>577152</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91060</t>
+          <t>89696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>95700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>136966</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>176754</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59757</t>
+          <t>59151</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>99506</t>
+          <t>98680</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20308</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27566</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42840</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45176</t>
+          <t>44259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>35342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>43244</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78527</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94927</t>
+          <t>93658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117338</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152351</t>
+          <t>151772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70643</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
